--- a/data/raw/portfolio_snapshots/Portfolio_2023.xlsx
+++ b/data/raw/portfolio_snapshots/Portfolio_2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c3b54154a9f56a2/Samir/Research/Portfolio/Portfolio Yearly/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yash/Library/CloudStorage/OneDrive-Personal/PMS-Decision-Platform/00_Original_Files/Portfolio_Snapshots/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="532" documentId="8_{EDF33660-9B23-4888-B529-2B640994E33F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB781ABF-2866-4490-9722-318E02CA8C09}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1B20CE-6A96-9A45-B901-2DD66B4F2EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="19" activeTab="25" xr2:uid="{D1491BFC-AA9E-4856-B603-CFD392162666}"/>
+    <workbookView xWindow="4420" yWindow="780" windowWidth="23260" windowHeight="13900" activeTab="2" xr2:uid="{D1491BFC-AA9E-4856-B603-CFD392162666}"/>
   </bookViews>
   <sheets>
     <sheet name="01Jan23" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
     <sheet name="Liquid" sheetId="3" r:id="rId27"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId28"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -54,7 +54,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -437,9 +436,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -477,7 +476,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -583,7 +582,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -725,7 +724,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -737,19 +736,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="41.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -758,11 +757,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -782,11 +781,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -806,7 +805,7 @@
         <v>6.5521298168756598E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -826,7 +825,7 @@
         <v>5.0588303880450505E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -846,7 +845,7 @@
         <v>7.4981577425383597E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -866,7 +865,7 @@
         <v>6.7180345583718604E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -886,7 +885,7 @@
         <v>1.2513860478731815E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -906,7 +905,7 @@
         <v>4.5310846696545524E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -926,7 +925,7 @@
         <v>4.5521797793271042E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -946,7 +945,7 @@
         <v>5.3524949585714507E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -966,7 +965,7 @@
         <v>1.6325566439329989E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -986,7 +985,7 @@
         <v>7.7820890890643091E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1006,7 +1005,7 @@
         <v>0.12035663625597091</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1026,7 +1025,7 @@
         <v>0.13491754910250547</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1046,7 +1045,7 @@
         <v>2.5788719544311806E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1066,7 +1065,7 @@
         <v>1.594233278325706E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1085,7 +1084,7 @@
         <v>5.2870976388406564E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1105,7 +1104,7 @@
         <v>0.13727734834962937</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1125,11 +1124,11 @@
         <v>3.5570006333735357E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B22" s="4"/>
       <c r="E22" s="3"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B23" s="4"/>
       <c r="D23">
         <f>SUM(D5:D21)</f>
@@ -1148,19 +1147,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1169,11 +1168,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1193,11 +1192,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -1217,7 +1216,7 @@
         <v>7.2439734424173965E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1240,7 +1239,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1260,7 +1259,7 @@
         <v>4.1629389834189567E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1280,7 +1279,7 @@
         <v>5.8873024759979874E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1300,7 +1299,7 @@
         <v>6.9847068979673702E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1320,7 +1319,7 @@
         <v>3.0699359945191934E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1340,7 +1339,7 @@
         <v>3.5252581956675764E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1360,7 +1359,7 @@
         <v>5.9324998664887905E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1380,7 +1379,7 @@
         <v>9.5524367895621506E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1400,7 +1399,7 @@
         <v>6.8056832934269618E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1420,7 +1419,7 @@
         <v>0.23460861409714182</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -1440,7 +1439,7 @@
         <v>4.8476997278715205E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -1460,7 +1459,7 @@
         <v>8.8715930469425122E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1483,11 +1482,11 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -1506,19 +1505,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1527,11 +1526,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1551,11 +1550,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -1575,7 +1574,7 @@
         <v>6.4869807338535493E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1598,7 +1597,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1618,7 +1617,7 @@
         <v>4.8317082642015396E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1638,7 +1637,7 @@
         <v>4.8714023613525774E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1658,7 +1657,7 @@
         <v>6.8588369286401982E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1678,7 +1677,7 @@
         <v>2.813843265961246E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1698,7 +1697,7 @@
         <v>3.6491658059928045E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1718,7 +1717,7 @@
         <v>6.7313063541689339E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1738,7 +1737,7 @@
         <v>8.0002395394758841E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1758,7 +1757,7 @@
         <v>6.0563240483710347E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1778,7 +1777,7 @@
         <v>0.28021973529594119</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -1798,7 +1797,7 @@
         <v>4.22974290547121E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -1818,7 +1817,7 @@
         <v>8.3915384372844917E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1841,11 +1840,11 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -1864,19 +1863,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1885,11 +1884,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1909,11 +1908,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -1933,7 +1932,7 @@
         <v>6.6725025952663816E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1953,7 +1952,7 @@
         <v>3.0309877003595134E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1973,7 +1972,7 @@
         <v>4.7304232075545134E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1993,7 +1992,7 @@
         <v>4.983916937945608E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -2013,7 +2012,7 @@
         <v>6.9082639559981465E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -2033,7 +2032,7 @@
         <v>2.8736329338934066E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -2056,7 +2055,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -2076,7 +2075,7 @@
         <v>6.8872867577970634E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -2096,7 +2095,7 @@
         <v>7.9726236515869187E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -2116,7 +2115,7 @@
         <v>6.0698998549498943E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -2136,7 +2135,7 @@
         <v>0.27672962403680973</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -2156,7 +2155,7 @@
         <v>4.3404369925818351E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -2176,7 +2175,7 @@
         <v>8.3373274816478105E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -2199,11 +2198,11 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -2222,19 +2221,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2243,11 +2242,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2267,11 +2266,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -2291,7 +2290,7 @@
         <v>6.5364792545824849E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -2311,7 +2310,7 @@
         <v>3.3082758938873226E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2331,7 +2330,7 @@
         <v>4.4563063782025104E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -2351,7 +2350,7 @@
         <v>5.3784318898774469E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -2371,7 +2370,7 @@
         <v>7.0210237436337086E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -2391,7 +2390,7 @@
         <v>2.7643405357404942E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -2411,7 +2410,7 @@
         <v>7.0972174419790299E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -2431,7 +2430,7 @@
         <v>8.1750240600841753E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -2451,7 +2450,7 @@
         <v>6.0596521927828988E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -2471,7 +2470,7 @@
         <v>0.27273208425997925</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -2491,7 +2490,7 @@
         <v>4.1964158584099617E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -2511,7 +2510,7 @@
         <v>8.2067490551255673E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>66</v>
       </c>
@@ -2533,7 +2532,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -2556,11 +2555,11 @@
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -2579,19 +2578,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2600,11 +2599,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2624,11 +2623,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -2648,7 +2647,7 @@
         <v>6.4771018070702971E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -2671,7 +2670,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2691,7 +2690,7 @@
         <v>4.5767404114799966E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -2711,7 +2710,7 @@
         <v>5.4340261079882567E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -2731,7 +2730,7 @@
         <v>7.0595916533391617E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -2754,7 +2753,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -2774,7 +2773,7 @@
         <v>7.1650048300939045E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -2794,7 +2793,7 @@
         <v>8.278473203037609E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -2814,7 +2813,7 @@
         <v>6.154756540513466E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -2834,7 +2833,7 @@
         <v>0.27547992518092568</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -2854,7 +2853,7 @@
         <v>4.1810147688887342E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -2874,7 +2873,7 @@
         <v>8.2699027030539787E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>66</v>
       </c>
@@ -2893,7 +2892,7 @@
         <v>6.1670352595512803E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -2915,7 +2914,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -2938,11 +2937,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -2961,19 +2960,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2982,11 +2981,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -3006,11 +3005,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -3030,7 +3029,7 @@
         <v>6.7493665556425095E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -3050,7 +3049,7 @@
         <v>4.4226784083412921E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3070,7 +3069,7 @@
         <v>5.3773499708229838E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -3090,7 +3089,7 @@
         <v>7.515446180328153E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -3110,7 +3109,7 @@
         <v>2.4549570963454139E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -3130,7 +3129,7 @@
         <v>6.5506371764126881E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -3150,7 +3149,7 @@
         <v>8.0994630601094908E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -3170,7 +3169,7 @@
         <v>5.717689352679161E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -3190,7 +3189,7 @@
         <v>0.27435844197385051</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -3213,7 +3212,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -3233,7 +3232,7 @@
         <v>7.6734673265525633E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>66</v>
       </c>
@@ -3252,7 +3251,7 @@
         <v>5.9997198687279707E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -3271,7 +3270,7 @@
         <v>5.613317714386043E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -3294,11 +3293,11 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -3317,19 +3316,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3338,11 +3337,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -3362,11 +3361,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -3386,7 +3385,7 @@
         <v>6.5031698059428725E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -3406,7 +3405,7 @@
         <v>4.5755241555266474E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3426,7 +3425,7 @@
         <v>5.3035324240180863E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -3446,7 +3445,7 @@
         <v>6.2321436288596696E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -3466,7 +3465,7 @@
         <v>2.5721293919746736E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -3486,7 +3485,7 @@
         <v>6.6111974016382219E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -3506,7 +3505,7 @@
         <v>7.8543953918109949E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -3526,7 +3525,7 @@
         <v>5.5424812925005167E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -3546,7 +3545,7 @@
         <v>0.28455069407835992</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -3566,7 +3565,7 @@
         <v>5.7269536496004629E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -3589,7 +3588,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>66</v>
       </c>
@@ -3608,7 +3607,7 @@
         <v>6.0512475484777541E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -3627,7 +3626,7 @@
         <v>6.0428896971241444E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -3650,11 +3649,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -3673,19 +3672,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3697,11 +3696,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -3721,11 +3720,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -3745,7 +3744,7 @@
         <v>6.4294412817780491E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -3765,7 +3764,7 @@
         <v>4.2327782308852681E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3785,7 +3784,7 @@
         <v>4.8066594061314354E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -3805,7 +3804,7 @@
         <v>4.7545680757693339E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -3828,7 +3827,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -3848,7 +3847,7 @@
         <v>6.2541114121003161E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -3868,7 +3867,7 @@
         <v>9.6892668634075238E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -3888,7 +3887,7 @@
         <v>5.7877019037324964E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -3908,7 +3907,7 @@
         <v>0.32035199110374851</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -3928,7 +3927,7 @@
         <v>5.0216698145648303E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -3948,7 +3947,7 @@
         <v>5.6355004449039833E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>66</v>
       </c>
@@ -3967,7 +3966,7 @@
         <v>5.4111488686503166E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -3986,7 +3985,7 @@
         <v>5.3502023221771881E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -4009,11 +4008,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -4032,19 +4031,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4056,11 +4055,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -4080,11 +4079,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -4104,7 +4103,7 @@
         <v>6.8773867335744462E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -4124,7 +4123,7 @@
         <v>4.0474389148844499E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4144,7 +4143,7 @@
         <v>5.0223734229621515E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -4164,7 +4163,7 @@
         <v>4.777576871736245E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -4184,7 +4183,7 @@
         <v>2.20343620617642E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -4204,7 +4203,7 @@
         <v>6.7320779245373941E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -4224,7 +4223,7 @@
         <v>9.7899189116396654E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -4244,7 +4243,7 @@
         <v>6.1524707672223386E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -4264,7 +4263,7 @@
         <v>0.30307205776571089</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -4284,7 +4283,7 @@
         <v>4.9300310457892405E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -4307,7 +4306,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>66</v>
       </c>
@@ -4326,7 +4325,7 @@
         <v>5.3766235631743688E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -4349,7 +4348,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -4372,11 +4371,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -4395,19 +4394,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4416,11 +4415,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -4440,11 +4439,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -4464,7 +4463,7 @@
         <v>7.5388858261955974E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -4484,7 +4483,7 @@
         <v>3.9523110895327923E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4504,7 +4503,7 @@
         <v>4.8570820994094897E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -4524,7 +4523,7 @@
         <v>4.8292602917887145E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -4544,7 +4543,7 @@
         <v>2.2537027580548222E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -4564,7 +4563,7 @@
         <v>6.4473185206724209E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -4588,7 +4587,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -4608,7 +4607,7 @@
         <v>5.6662666219249563E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -4628,7 +4627,7 @@
         <v>0.31354774543321895</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -4648,7 +4647,7 @@
         <v>4.8638599830828522E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -4668,7 +4667,7 @@
         <v>5.0352343390944652E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>66</v>
       </c>
@@ -4687,7 +4686,7 @@
         <v>5.7020816464431016E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -4707,7 +4706,7 @@
         <v>5.8636901004402824E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -4727,11 +4726,11 @@
         <v>2.4222503068907664E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -4750,19 +4749,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4771,11 +4770,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -4795,11 +4794,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -4819,7 +4818,7 @@
         <v>7.3599957457792853E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -4845,7 +4844,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4865,7 +4864,7 @@
         <v>7.4285307188982241E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -4885,7 +4884,7 @@
         <v>6.4209001048896777E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -4905,7 +4904,7 @@
         <v>1.0944495500497694E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -4925,7 +4924,7 @@
         <v>4.5109517096649482E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -4945,7 +4944,7 @@
         <v>4.3612908690632758E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -4965,7 +4964,7 @@
         <v>5.5193596129185007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -4985,7 +4984,7 @@
         <v>1.5714816552836242E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -5005,7 +5004,7 @@
         <v>9.3811129362162016E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -5025,7 +5024,7 @@
         <v>0.10516080536894222</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -5045,7 +5044,7 @@
         <v>0.14225533235211932</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -5065,7 +5064,7 @@
         <v>2.3199076692122532E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -5085,7 +5084,7 @@
         <v>1.6088278974467244E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -5104,7 +5103,7 @@
         <v>5.020952053446999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -5124,7 +5123,7 @@
         <v>0.13222953357978273</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -5147,11 +5146,11 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B22" s="4"/>
       <c r="E22" s="3"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B23" s="4"/>
       <c r="D23">
         <f>SUM(D5:D21)</f>
@@ -5170,19 +5169,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5191,11 +5190,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -5215,11 +5214,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -5239,7 +5238,7 @@
         <v>8.1189055337625701E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -5259,7 +5258,7 @@
         <v>3.9938157495499671E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -5279,7 +5278,7 @@
         <v>4.605549111280912E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -5299,7 +5298,7 @@
         <v>5.1111235277349447E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -5319,7 +5318,7 @@
         <v>2.2029392669983168E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -5339,7 +5338,7 @@
         <v>6.0931322788320003E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -5359,7 +5358,7 @@
         <v>0.10703141735608176</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -5379,7 +5378,7 @@
         <v>5.3678383564611722E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -5402,7 +5401,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -5422,7 +5421,7 @@
         <v>4.772650128274758E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -5442,7 +5441,7 @@
         <v>4.7826753897163558E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>66</v>
       </c>
@@ -5461,7 +5460,7 @@
         <v>5.4915656989490642E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -5481,7 +5480,7 @@
         <v>5.4188433410625132E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -5504,11 +5503,11 @@
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -5527,19 +5526,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5548,11 +5547,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -5572,11 +5571,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -5596,7 +5595,7 @@
         <v>8.1165827308386396E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -5616,7 +5615,7 @@
         <v>3.745850570612011E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -5636,7 +5635,7 @@
         <v>4.6136723450257648E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -5656,7 +5655,7 @@
         <v>4.847468926269622E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -5676,7 +5675,7 @@
         <v>2.2421816133002266E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -5696,7 +5695,7 @@
         <v>5.6460679364015103E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -5716,7 +5715,7 @@
         <v>0.10966970308927836</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -5736,7 +5735,7 @@
         <v>5.8112662960918014E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -5756,7 +5755,7 @@
         <v>0.23787268980366683</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -5776,7 +5775,7 @@
         <v>4.8908624427685003E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -5796,7 +5795,7 @@
         <v>4.8822105606373109E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>66</v>
       </c>
@@ -5815,7 +5814,7 @@
         <v>5.428026479532666E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -5838,7 +5837,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -5861,11 +5860,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -5884,19 +5883,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5905,11 +5904,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -5929,11 +5928,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -5953,7 +5952,7 @@
         <v>7.9461181023247729E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -5973,7 +5972,7 @@
         <v>3.7887234775697685E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -5993,7 +5992,7 @@
         <v>4.6810673090857284E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -6013,7 +6012,7 @@
         <v>4.8608638448791909E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -6033,7 +6032,7 @@
         <v>2.2615358784701545E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -6053,7 +6052,7 @@
         <v>5.4288682781101202E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6073,7 +6072,7 @@
         <v>0.10850846297095845</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>88</v>
       </c>
@@ -6095,7 +6094,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -6115,7 +6114,7 @@
         <v>5.8453334975651854E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -6138,7 +6137,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -6158,7 +6157,7 @@
         <v>4.7350446565908672E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -6178,7 +6177,7 @@
         <v>4.8857318216875771E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>66</v>
       </c>
@@ -6197,7 +6196,7 @@
         <v>5.3961057964620737E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -6217,7 +6216,7 @@
         <v>7.1280596700311963E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -6240,11 +6239,11 @@
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -6263,19 +6262,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6284,11 +6283,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -6308,11 +6307,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -6332,7 +6331,7 @@
         <v>8.2145562380889478E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -6352,7 +6351,7 @@
         <v>3.7997483495581956E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -6372,7 +6371,7 @@
         <v>4.1400854184288127E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -6392,7 +6391,7 @@
         <v>4.9879996208092192E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -6412,7 +6411,7 @@
         <v>2.1621223770681656E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -6432,7 +6431,7 @@
         <v>5.8667508772525093E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6452,7 +6451,7 @@
         <v>9.7368837289661045E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>88</v>
       </c>
@@ -6471,7 +6470,7 @@
         <v>5.0865958891056662E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -6494,7 +6493,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -6517,7 +6516,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -6537,7 +6536,7 @@
         <v>4.9143847151590751E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -6560,7 +6559,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>66</v>
       </c>
@@ -6583,7 +6582,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -6603,7 +6602,7 @@
         <v>6.947419514533125E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -6626,11 +6625,11 @@
         <v>98</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -6649,19 +6648,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6670,11 +6669,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -6694,11 +6693,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -6718,7 +6717,7 @@
         <v>8.6994282981609231E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -6738,7 +6737,7 @@
         <v>3.8058819057815718E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -6758,7 +6757,7 @@
         <v>4.0573085612657607E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -6778,7 +6777,7 @@
         <v>4.3430157664768855E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -6798,7 +6797,7 @@
         <v>2.0199401398261096E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -6818,7 +6817,7 @@
         <v>5.6918643367639743E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6838,7 +6837,7 @@
         <v>8.4545740006486042E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>88</v>
       </c>
@@ -6857,7 +6856,7 @@
         <v>4.9281424661612651E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -6880,7 +6879,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -6900,7 +6899,7 @@
         <v>0.22715534273841517</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -6920,7 +6919,7 @@
         <v>4.3374191166398485E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -6940,7 +6939,7 @@
         <v>3.9187953510331955E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>66</v>
       </c>
@@ -6960,7 +6959,7 @@
         <v>7.0063981341213902E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -6980,7 +6979,7 @@
         <v>6.8679897902566747E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -7003,11 +7002,11 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -7026,19 +7025,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7047,11 +7046,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -7071,11 +7070,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -7095,7 +7094,7 @@
         <v>8.9802934957088798E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -7115,7 +7114,7 @@
         <v>3.7066986279735162E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -7135,7 +7134,7 @@
         <v>4.0956064876211534E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -7155,7 +7154,7 @@
         <v>4.2953738832032747E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -7175,7 +7174,7 @@
         <v>1.8876408636510588E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -7195,7 +7194,7 @@
         <v>5.9095307277153834E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -7215,7 +7214,7 @@
         <v>8.6210633003389769E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>88</v>
       </c>
@@ -7238,7 +7237,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -7258,7 +7257,7 @@
         <v>4.504199489270571E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -7278,7 +7277,7 @@
         <v>0.22747551214935219</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -7298,7 +7297,7 @@
         <v>4.3629959102058545E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -7318,7 +7317,7 @@
         <v>3.9527783595118271E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>66</v>
       </c>
@@ -7338,7 +7337,7 @@
         <v>6.9177479653111482E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -7358,7 +7357,7 @@
         <v>7.0027983676258052E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -7381,11 +7380,11 @@
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -7404,19 +7403,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7425,11 +7424,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -7449,11 +7448,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -7473,7 +7472,7 @@
         <v>8.6206866795462078E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -7493,7 +7492,7 @@
         <v>4.3315041166930184E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -7513,7 +7512,7 @@
         <v>3.8668365206874888E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -7533,7 +7532,7 @@
         <v>4.4705542676157312E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -7553,7 +7552,7 @@
         <v>1.7865489961984695E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -7573,7 +7572,7 @@
         <v>5.5812367058372454E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -7593,7 +7592,7 @@
         <v>0.12308335400645683</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>88</v>
       </c>
@@ -7613,7 +7612,7 @@
         <v>5.77659753769975E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -7633,7 +7632,7 @@
         <v>4.3499312533629576E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -7653,7 +7652,7 @@
         <v>0.22415604405455763</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -7673,7 +7672,7 @@
         <v>4.0811908476403029E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -7693,7 +7692,7 @@
         <v>3.9417597362396521E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>66</v>
       </c>
@@ -7713,7 +7712,7 @@
         <v>6.2655425230954853E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -7733,7 +7732,7 @@
         <v>6.6128682566689259E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -7756,11 +7755,11 @@
         <v>104</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -7776,17 +7775,17 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C18A242-0910-4E92-A461-DA397E54CBAB}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -7798,7 +7797,7 @@
         <v>126.934</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -7810,7 +7809,7 @@
         <v>1.8760000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -7822,7 +7821,7 @@
         <v>1.8760000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -7834,7 +7833,7 @@
         <v>75.95</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -7846,7 +7845,7 @@
         <v>928.30000000000007</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -7858,7 +7857,7 @@
         <v>2305.9700000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -7870,7 +7869,7 @@
         <v>3192.904</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -7882,7 +7881,7 @@
         <v>454.53800000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -7894,7 +7893,7 @@
         <v>1899.2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -7906,7 +7905,7 @@
         <v>1899.2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -7918,7 +7917,7 @@
         <v>4065.6959999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -7930,7 +7929,7 @@
         <v>5239.8760000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C16" s="2">
         <f>SUM(C3:C15)</f>
         <v>20192.32</v>
@@ -7945,7 +7944,7 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E270A1E4-8160-48C8-BABC-214DD704FB6A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7957,19 +7956,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7978,11 +7977,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -8002,11 +8001,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -8023,10 +8022,10 @@
       </c>
       <c r="E5" s="3">
         <f t="shared" ref="E5:E21" si="0">D5/$D$23</f>
-        <v>7.0114127323948852E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>7.1319595387765874E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -8043,10 +8042,10 @@
       </c>
       <c r="E6" s="3">
         <f t="shared" si="0"/>
-        <v>4.1584106946121031E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>4.2299060048999894E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -8063,10 +8062,10 @@
       </c>
       <c r="E7" s="3">
         <f t="shared" si="0"/>
-        <v>6.5605596993241741E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>6.6733550160477273E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -8083,10 +8082,10 @@
       </c>
       <c r="E8" s="3">
         <f t="shared" si="0"/>
-        <v>6.3733024058373625E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>6.4828782189368855E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -8109,7 +8108,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -8126,10 +8125,10 @@
       </c>
       <c r="E10" s="3">
         <f t="shared" si="0"/>
-        <v>4.8562534403842901E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>4.9397467199217684E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -8146,10 +8145,10 @@
       </c>
       <c r="E11" s="3">
         <f t="shared" si="0"/>
-        <v>4.5520510287911299E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>4.6303141741729427E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -8166,33 +8165,32 @@
       </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>4.7694776144685314E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>4.8514789623390946E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>15</v>
       </c>
       <c r="B13" s="4">
-        <f>1727-863-216</f>
-        <v>648</v>
+        <v>0</v>
       </c>
       <c r="C13" s="2">
         <v>611.9</v>
       </c>
       <c r="D13">
         <f t="shared" si="1"/>
-        <v>396511.2</v>
+        <v>0</v>
       </c>
       <c r="E13" s="3">
         <f t="shared" si="0"/>
-        <v>1.6902340195045579E-2</v>
+        <v>0</v>
       </c>
       <c r="G13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -8209,10 +8207,10 @@
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>9.8948619946386998E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.10064983774452103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -8229,10 +8227,10 @@
       </c>
       <c r="E15" s="3">
         <f t="shared" si="0"/>
-        <v>0.10850599458238817</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.11037153176004473</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -8249,10 +8247,10 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>0.14015171670440404</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.14256133691968101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -8269,10 +8267,10 @@
       </c>
       <c r="E17" s="3">
         <f t="shared" si="0"/>
-        <v>2.1876816304171973E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>2.225294311911221E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -8295,7 +8293,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -8311,10 +8309,10 @@
       </c>
       <c r="E19" s="3">
         <f t="shared" si="0"/>
-        <v>5.5079594292630984E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>5.6026574515047389E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -8331,10 +8329,10 @@
       </c>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>0.12529481947995313</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.12744900593580041</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -8351,21 +8349,21 @@
       </c>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>5.0425422336894329E-2</v>
+        <v>5.1292383654843295E-2</v>
       </c>
       <c r="G21" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B22" s="4"/>
       <c r="E22" s="3"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B23" s="4"/>
       <c r="D23">
         <f>SUM(D5:D21)</f>
-        <v>23458952.75</v>
+        <v>23062441.549999997</v>
       </c>
     </row>
   </sheetData>
@@ -8380,19 +8378,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8401,11 +8399,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -8425,11 +8423,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -8451,7 +8449,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -8471,7 +8469,7 @@
         <v>7.1350770455332391E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -8491,7 +8489,7 @@
         <v>4.231754972281055E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -8511,7 +8509,7 @@
         <v>6.6762720585854696E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -8531,7 +8529,7 @@
         <v>6.4857120006682881E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -8551,7 +8549,7 @@
         <v>4.9419059713437338E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -8571,7 +8569,7 @@
         <v>4.6323381671085337E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -8591,7 +8589,7 @@
         <v>4.8535996303494235E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -8611,7 +8609,7 @@
         <v>0.1006938335843065</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -8631,7 +8629,7 @@
         <v>0.11041977712573044</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -8651,7 +8649,7 @@
         <v>0.14262365302350466</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -8671,7 +8669,7 @@
         <v>2.2262670277567332E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -8690,7 +8688,7 @@
         <v>5.6051064730345594E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -8710,7 +8708,7 @@
         <v>0.12750471617012987</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -8733,11 +8731,11 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -8756,19 +8754,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8777,11 +8775,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -8801,11 +8799,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -8824,7 +8822,7 @@
         <v>4.2099644043829064E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -8844,7 +8842,7 @@
         <v>6.4267524587005173E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -8864,7 +8862,7 @@
         <v>4.5925920052905481E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -8884,7 +8882,7 @@
         <v>6.6215615610525996E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -8904,7 +8902,7 @@
         <v>6.1042361492457696E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -8924,7 +8922,7 @@
         <v>3.9737538109024119E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -8944,7 +8942,7 @@
         <v>3.4706000959483063E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -8964,7 +8962,7 @@
         <v>6.0556428084807865E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -8984,7 +8982,7 @@
         <v>0.1044141256688586</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -9004,7 +9002,7 @@
         <v>0.10009219034773438</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -9024,7 +9022,7 @@
         <v>0.17764052442068692</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -9044,7 +9042,7 @@
         <v>1.9098633103246627E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -9063,7 +9061,7 @@
         <v>3.8062245698182916E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -9089,7 +9087,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -9112,11 +9110,11 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -9135,19 +9133,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9156,11 +9154,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -9180,11 +9178,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -9203,7 +9201,7 @@
         <v>4.2564270044788688E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -9229,7 +9227,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -9249,7 +9247,7 @@
         <v>4.3400571281146536E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -9269,7 +9267,7 @@
         <v>6.6612575436105839E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -9289,7 +9287,7 @@
         <v>6.0589245186324463E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -9309,7 +9307,7 @@
         <v>3.6667317002348522E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -9329,7 +9327,7 @@
         <v>3.470730263780205E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -9349,7 +9347,7 @@
         <v>5.7922460594562963E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -9369,7 +9367,7 @@
         <v>0.10794801516561595</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -9389,7 +9387,7 @@
         <v>9.9060160957756924E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -9409,7 +9407,7 @@
         <v>0.19914026103656915</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -9429,7 +9427,7 @@
         <v>1.8079186953024545E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -9448,7 +9446,7 @@
         <v>3.3902861858966939E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -9468,7 +9466,7 @@
         <v>0.13519060473399733</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -9491,11 +9489,11 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -9514,19 +9512,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9535,11 +9533,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -9559,11 +9557,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -9586,7 +9584,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -9606,7 +9604,7 @@
         <v>5.5816259099599239E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -9626,7 +9624,7 @@
         <v>4.6030903074073204E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -9646,7 +9644,7 @@
         <v>5.858741556942465E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -9666,7 +9664,7 @@
         <v>6.988931591514036E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -9686,7 +9684,7 @@
         <v>3.5488596550605114E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -9706,7 +9704,7 @@
         <v>3.3416777189733342E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -9726,7 +9724,7 @@
         <v>6.8205621992278059E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -9746,7 +9744,7 @@
         <v>0.10814477777826351</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -9769,7 +9767,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -9789,7 +9787,7 @@
         <v>0.18750042960722105</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -9812,7 +9810,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -9831,7 +9829,7 @@
         <v>3.8823235055846284E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -9851,7 +9849,7 @@
         <v>0.13372377133755631</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -9874,11 +9872,11 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -9897,19 +9895,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9918,11 +9916,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -9942,11 +9940,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -9966,7 +9964,7 @@
         <v>7.9209777541105267E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -9986,7 +9984,7 @@
         <v>5.732355737466692E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -10006,7 +10004,7 @@
         <v>4.6820177499256363E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -10026,7 +10024,7 @@
         <v>6.0897344785313973E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -10046,7 +10044,7 @@
         <v>7.2156541231088861E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -10066,7 +10064,7 @@
         <v>3.5080304713496831E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -10086,7 +10084,7 @@
         <v>3.3042050399742715E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -10106,7 +10104,7 @@
         <v>6.7777192666563804E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -10126,7 +10124,7 @@
         <v>0.10610010043673311</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -10146,7 +10144,7 @@
         <v>7.0126392348995314E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -10166,7 +10164,7 @@
         <v>0.18211134183776867</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -10185,7 +10183,7 @@
         <v>3.8987066559362987E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -10208,7 +10206,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -10231,11 +10229,11 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -10254,19 +10252,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10275,11 +10273,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -10299,11 +10297,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -10323,7 +10321,7 @@
         <v>7.8460066748204521E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -10343,7 +10341,7 @@
         <v>5.2240048013344149E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -10363,7 +10361,7 @@
         <v>4.901846779378928E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -10383,7 +10381,7 @@
         <v>6.0292590715831526E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -10403,7 +10401,7 @@
         <v>7.0878565844423577E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -10423,7 +10421,7 @@
         <v>3.4327445208782066E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -10443,7 +10441,7 @@
         <v>3.3770921645260001E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -10463,7 +10461,7 @@
         <v>6.430779772866238E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -10483,7 +10481,7 @@
         <v>9.7399295780519424E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -10503,7 +10501,7 @@
         <v>7.2390497082646305E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -10523,7 +10521,7 @@
         <v>0.18935106420135733</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -10546,7 +10544,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -10566,7 +10564,7 @@
         <v>0.1078290187756383</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -10589,11 +10587,11 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>

--- a/data/raw/portfolio_snapshots/Portfolio_2023.xlsx
+++ b/data/raw/portfolio_snapshots/Portfolio_2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yash/Library/CloudStorage/OneDrive-Personal/PMS-Decision-Platform/00_Original_Files/Portfolio_Snapshots/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c3b54154a9f56a2/Samir/Research/Portfolio/Portfolio Yearly/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1B20CE-6A96-9A45-B901-2DD66B4F2EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="533" documentId="8_{EDF33660-9B23-4888-B529-2B640994E33F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6641DEE-883B-4770-B1FC-09697E7ADCB5}"/>
   <bookViews>
-    <workbookView xWindow="4420" yWindow="780" windowWidth="23260" windowHeight="13900" activeTab="2" xr2:uid="{D1491BFC-AA9E-4856-B603-CFD392162666}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="25" activeTab="2" xr2:uid="{D1491BFC-AA9E-4856-B603-CFD392162666}"/>
   </bookViews>
   <sheets>
     <sheet name="01Jan23" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
     <sheet name="Liquid" sheetId="3" r:id="rId27"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId28"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -54,6 +54,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -136,6 +137,213 @@
     <t>LiquidBees</t>
   </si>
   <si>
+    <t>Right Issue 1:1 at face value of Rs5. 3372*5 = 16860</t>
+  </si>
+  <si>
+    <t>Price is changed to closing price of 20/1/23</t>
+  </si>
+  <si>
+    <t>Less 16.86</t>
+  </si>
+  <si>
+    <t>Sell 36000@7.88 = 283680</t>
+  </si>
+  <si>
+    <t>Sell 648@580.82 = 376371</t>
+  </si>
+  <si>
+    <t>Sell 1533@299.68 = 459409</t>
+  </si>
+  <si>
+    <t>Add 1119.46</t>
+  </si>
+  <si>
+    <t>AstraMicro</t>
+  </si>
+  <si>
+    <t>Buy 4326@273.23 = 1181992.98</t>
+  </si>
+  <si>
+    <t>Less 1181.99</t>
+  </si>
+  <si>
+    <t>Approx 53@698.83 = 37038</t>
+  </si>
+  <si>
+    <t>VRL Buyback at 700</t>
+  </si>
+  <si>
+    <t>Add 37.038</t>
+  </si>
+  <si>
+    <t>Approx 147@499.17 = 73378</t>
+  </si>
+  <si>
+    <t>GPIL Buyback at 500</t>
+  </si>
+  <si>
+    <t>Add 73.378</t>
+  </si>
+  <si>
+    <t>Buy 2424@336.75 = 816282</t>
+  </si>
+  <si>
+    <t>Sell 246@2708 = 666168</t>
+  </si>
+  <si>
+    <t>Sell 16088@31.26 = 502911</t>
+  </si>
+  <si>
+    <t>Add 352.797</t>
+  </si>
+  <si>
+    <t>Sell 1428@698.65 = 997672</t>
+  </si>
+  <si>
+    <t>Add 997.672</t>
+  </si>
+  <si>
+    <t>Buy 115@2685.54 = 308837</t>
+  </si>
+  <si>
+    <t>Less 308.837</t>
+  </si>
+  <si>
+    <t>Sell 849@522.34 = 443466.66</t>
+  </si>
+  <si>
+    <t>Add 443.467</t>
+  </si>
+  <si>
+    <t>Sell 1304@545.95 = 711919</t>
+  </si>
+  <si>
+    <t>Add 711.919</t>
+  </si>
+  <si>
+    <t>Sell 1269@1010.85 = 1282768</t>
+  </si>
+  <si>
+    <t>Add 1282.768</t>
+  </si>
+  <si>
+    <t>WelEnt</t>
+  </si>
+  <si>
+    <t>Add 6%. 7985@285.12 = 2276683</t>
+  </si>
+  <si>
+    <t>Less 2276.683</t>
+  </si>
+  <si>
+    <t>Sell 2092@561.88 = 1175453</t>
+  </si>
+  <si>
+    <t>Sell 217@813.59 = 176549</t>
+  </si>
+  <si>
+    <t>ZenTech</t>
+  </si>
+  <si>
+    <t>Add 6%. 2592@729.25 = 1890216</t>
+  </si>
+  <si>
+    <t>Less 538.214</t>
+  </si>
+  <si>
+    <t>Add till 6%. 189@2904.62 = 548973</t>
+  </si>
+  <si>
+    <t>Less 548.973</t>
+  </si>
+  <si>
+    <t>Sell 925@684.08 = 632774</t>
+  </si>
+  <si>
+    <t>Add 632.774</t>
+  </si>
+  <si>
+    <t>Price of 5/9/23</t>
+  </si>
+  <si>
+    <t>Sell 171@884.38 = 151229</t>
+  </si>
+  <si>
+    <t>Add 151.229</t>
+  </si>
+  <si>
+    <t>Price of 13/9/23</t>
+  </si>
+  <si>
+    <t>Sell 484@698.81 = 338224</t>
+  </si>
+  <si>
+    <t>Buy 518@772 = 399896</t>
+  </si>
+  <si>
+    <t>Less 61.672</t>
+  </si>
+  <si>
+    <t>Split 10 to 5, Shares double</t>
+  </si>
+  <si>
+    <t>Sell 3258@831.52 = 2709092</t>
+  </si>
+  <si>
+    <t>Add 2709.092</t>
+  </si>
+  <si>
+    <t>Add 820@710.33 = 582471</t>
+  </si>
+  <si>
+    <t>Less 582.471</t>
+  </si>
+  <si>
+    <t>ThomasCook</t>
+  </si>
+  <si>
+    <t>Buy 13763@142.45 = 1960539</t>
+  </si>
+  <si>
+    <t>Sell 1143@802.42 = 917166</t>
+  </si>
+  <si>
+    <t>Less 1043.373</t>
+  </si>
+  <si>
+    <t>Sell 74@3247.12 = 240287</t>
+  </si>
+  <si>
+    <t>Sell 1205@802.42 = 966916</t>
+  </si>
+  <si>
+    <t>Sell 459@660.25 = 303055</t>
+  </si>
+  <si>
+    <t>Buy 1084@289.05 = 313330</t>
+  </si>
+  <si>
+    <t>Add 1196.928</t>
+  </si>
+  <si>
+    <t>Sell 85@3470.7 = 295009</t>
+  </si>
+  <si>
+    <t>Add 295.009</t>
+  </si>
+  <si>
+    <t>Buy 6317@143.24 = 904847</t>
+  </si>
+  <si>
+    <t>Less 904.847</t>
+  </si>
+  <si>
+    <t>Add 20.192</t>
+  </si>
+  <si>
+    <t>LiquidFund Value for 2023</t>
+  </si>
+  <si>
     <t>Jan</t>
   </si>
   <si>
@@ -171,219 +379,12 @@
   <si>
     <t>Dec</t>
   </si>
-  <si>
-    <t>Right Issue 1:1 at face value of Rs5. 3372*5 = 16860</t>
-  </si>
-  <si>
-    <t>Less 16.86</t>
-  </si>
-  <si>
-    <t>Price is changed to closing price of 20/1/23</t>
-  </si>
-  <si>
-    <t>Sell 36000@7.88 = 283680</t>
-  </si>
-  <si>
-    <t>Sell 1533@299.68 = 459409</t>
-  </si>
-  <si>
-    <t>AstraMicro</t>
-  </si>
-  <si>
-    <t>Sell 648@580.82 = 376371</t>
-  </si>
-  <si>
-    <t>Add 1119.46</t>
-  </si>
-  <si>
-    <t>Buy 4326@273.23 = 1181992.98</t>
-  </si>
-  <si>
-    <t>Less 1181.99</t>
-  </si>
-  <si>
-    <t>VRL Buyback at 700</t>
-  </si>
-  <si>
-    <t>GPIL Buyback at 500</t>
-  </si>
-  <si>
-    <t>Approx 147@499.17 = 73378</t>
-  </si>
-  <si>
-    <t>Approx 53@698.83 = 37038</t>
-  </si>
-  <si>
-    <t>Add 37.038</t>
-  </si>
-  <si>
-    <t>Add 73.378</t>
-  </si>
-  <si>
-    <t>Sell 246@2708 = 666168</t>
-  </si>
-  <si>
-    <t>Sell 16088@31.26 = 502911</t>
-  </si>
-  <si>
-    <t>Sell 1428@698.65 = 997672</t>
-  </si>
-  <si>
-    <t>Add 997.672</t>
-  </si>
-  <si>
-    <t>Buy 2424@336.75 = 816282</t>
-  </si>
-  <si>
-    <t>Add 352.797</t>
-  </si>
-  <si>
-    <t>Buy 115@2685.54 = 308837</t>
-  </si>
-  <si>
-    <t>Less 308.837</t>
-  </si>
-  <si>
-    <t>Sell 849@522.34 = 443466.66</t>
-  </si>
-  <si>
-    <t>Add 443.467</t>
-  </si>
-  <si>
-    <t>Sell 1304@545.95 = 711919</t>
-  </si>
-  <si>
-    <t>Add 711.919</t>
-  </si>
-  <si>
-    <t>Sell 1269@1010.85 = 1282768</t>
-  </si>
-  <si>
-    <t>Add 1282.768</t>
-  </si>
-  <si>
-    <t>WelEnt</t>
-  </si>
-  <si>
-    <t>ZenTech</t>
-  </si>
-  <si>
-    <t>Sell 2092@561.88 = 1175453</t>
-  </si>
-  <si>
-    <t>Sell 217@813.59 = 176549</t>
-  </si>
-  <si>
-    <t>Add till 6%. 189@2904.62 = 548973</t>
-  </si>
-  <si>
-    <t>Less 548.973</t>
-  </si>
-  <si>
-    <t>Add 6%. 7985@285.12 = 2276683</t>
-  </si>
-  <si>
-    <t>Less 2276.683</t>
-  </si>
-  <si>
-    <t>Add 6%. 2592@729.25 = 1890216</t>
-  </si>
-  <si>
-    <t>Less 538.214</t>
-  </si>
-  <si>
-    <t>Sell 925@684.08 = 632774</t>
-  </si>
-  <si>
-    <t>Add 632.774</t>
-  </si>
-  <si>
-    <t>Sell 171@884.38 = 151229</t>
-  </si>
-  <si>
-    <t>Add 151.229</t>
-  </si>
-  <si>
-    <t>Price of 5/9/23</t>
-  </si>
-  <si>
-    <t>Sell 484@698.81 = 338224</t>
-  </si>
-  <si>
-    <t>Buy 518@772 = 399896</t>
-  </si>
-  <si>
-    <t>Less 61.672</t>
-  </si>
-  <si>
-    <t>Price of 13/9/23</t>
-  </si>
-  <si>
-    <t>Split 10 to 5, Shares double</t>
-  </si>
-  <si>
-    <t>Sell 3258@831.52 = 2709092</t>
-  </si>
-  <si>
-    <t>Add 2709.092</t>
-  </si>
-  <si>
-    <t>ThomasCook</t>
-  </si>
-  <si>
-    <t>Buy 13763@142.45 = 1960539</t>
-  </si>
-  <si>
-    <t>Add 820@710.33 = 582471</t>
-  </si>
-  <si>
-    <t>Less 582.471</t>
-  </si>
-  <si>
-    <t>Sell 1143@802.42 = 917166</t>
-  </si>
-  <si>
-    <t>Less 1043.373</t>
-  </si>
-  <si>
-    <t>Sell 74@3247.12 = 240287</t>
-  </si>
-  <si>
-    <t>Sell 459@660.25 = 303055</t>
-  </si>
-  <si>
-    <t>Buy 1084@289.05 = 313330</t>
-  </si>
-  <si>
-    <t>Sell 1205@802.42 = 966916</t>
-  </si>
-  <si>
-    <t>Add 1196.928</t>
-  </si>
-  <si>
-    <t>Sell 85@3470.7 = 295009</t>
-  </si>
-  <si>
-    <t>Add 295.009</t>
-  </si>
-  <si>
-    <t>Buy 6317@143.24 = 904847</t>
-  </si>
-  <si>
-    <t>Less 904.847</t>
-  </si>
-  <si>
-    <t>LiquidFund Value for 2023</t>
-  </si>
-  <si>
-    <t>Add 20.192</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -736,19 +737,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="41.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -757,11 +758,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -781,11 +782,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -805,7 +806,7 @@
         <v>6.5521298168756598E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -825,7 +826,7 @@
         <v>5.0588303880450505E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -845,7 +846,7 @@
         <v>7.4981577425383597E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -865,7 +866,7 @@
         <v>6.7180345583718604E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -885,7 +886,7 @@
         <v>1.2513860478731815E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -905,7 +906,7 @@
         <v>4.5310846696545524E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -925,7 +926,7 @@
         <v>4.5521797793271042E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -945,7 +946,7 @@
         <v>5.3524949585714507E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -965,7 +966,7 @@
         <v>1.6325566439329989E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -985,7 +986,7 @@
         <v>7.7820890890643091E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1005,7 +1006,7 @@
         <v>0.12035663625597091</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1025,7 +1026,7 @@
         <v>0.13491754910250547</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1045,7 +1046,7 @@
         <v>2.5788719544311806E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1065,7 +1066,7 @@
         <v>1.594233278325706E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1084,7 +1085,7 @@
         <v>5.2870976388406564E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1104,7 +1105,7 @@
         <v>0.13727734834962937</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1124,11 +1125,11 @@
         <v>3.5570006333735357E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5">
       <c r="B22" s="4"/>
       <c r="E22" s="3"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5">
       <c r="B23" s="4"/>
       <c r="D23">
         <f>SUM(D5:D21)</f>
@@ -1147,19 +1148,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1168,11 +1169,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1192,13 +1193,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -1216,7 +1217,7 @@
         <v>7.2439734424173965E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1236,10 +1237,10 @@
         <v>4.9835815924422884E-2</v>
       </c>
       <c r="G6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1259,7 +1260,7 @@
         <v>4.1629389834189567E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1279,7 +1280,7 @@
         <v>5.8873024759979874E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1299,7 +1300,7 @@
         <v>6.9847068979673702E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1319,7 +1320,7 @@
         <v>3.0699359945191934E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1339,7 +1340,7 @@
         <v>3.5252581956675764E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1359,7 +1360,7 @@
         <v>5.9324998664887905E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1379,7 +1380,7 @@
         <v>9.5524367895621506E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1399,7 +1400,7 @@
         <v>6.8056832934269618E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1419,7 +1420,7 @@
         <v>0.23460861409714182</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -1439,7 +1440,7 @@
         <v>4.8476997278715205E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -1459,7 +1460,7 @@
         <v>8.8715930469425122E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1479,14 +1480,14 @@
         <v>4.6715282835631061E-2</v>
       </c>
       <c r="G18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -1505,19 +1506,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1526,11 +1527,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1550,13 +1551,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -1574,7 +1575,7 @@
         <v>6.4869807338535493E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1594,10 +1595,10 @@
         <v>2.9989803865585748E-2</v>
       </c>
       <c r="G6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1617,7 +1618,7 @@
         <v>4.8317082642015396E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1637,7 +1638,7 @@
         <v>4.8714023613525774E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1657,7 +1658,7 @@
         <v>6.8588369286401982E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1677,7 +1678,7 @@
         <v>2.813843265961246E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1697,7 +1698,7 @@
         <v>3.6491658059928045E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1717,7 +1718,7 @@
         <v>6.7313063541689339E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1737,7 +1738,7 @@
         <v>8.0002395394758841E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1757,7 +1758,7 @@
         <v>6.0563240483710347E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1777,7 +1778,7 @@
         <v>0.28021973529594119</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -1797,7 +1798,7 @@
         <v>4.22974290547121E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -1817,7 +1818,7 @@
         <v>8.3915384372844917E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1837,14 +1838,14 @@
         <v>6.0579574390738446E-2</v>
       </c>
       <c r="G18" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -1863,19 +1864,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1884,11 +1885,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1908,13 +1909,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -1932,7 +1933,7 @@
         <v>6.6725025952663816E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1952,7 +1953,7 @@
         <v>3.0309877003595134E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1972,7 +1973,7 @@
         <v>4.7304232075545134E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1992,7 +1993,7 @@
         <v>4.983916937945608E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -2012,7 +2013,7 @@
         <v>6.9082639559981465E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -2032,7 +2033,7 @@
         <v>2.8736329338934066E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -2052,10 +2053,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -2075,7 +2076,7 @@
         <v>6.8872867577970634E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -2095,7 +2096,7 @@
         <v>7.9726236515869187E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -2115,7 +2116,7 @@
         <v>6.0698998549498943E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -2135,7 +2136,7 @@
         <v>0.27672962403680973</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -2155,7 +2156,7 @@
         <v>4.3404369925818351E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -2175,7 +2176,7 @@
         <v>8.3373274816478105E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -2195,14 +2196,14 @@
         <v>9.5197355267379269E-2</v>
       </c>
       <c r="G18" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -2221,19 +2222,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2242,11 +2243,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2266,13 +2267,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -2290,7 +2291,7 @@
         <v>6.5364792545824849E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -2310,7 +2311,7 @@
         <v>3.3082758938873226E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2330,7 +2331,7 @@
         <v>4.4563063782025104E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -2350,7 +2351,7 @@
         <v>5.3784318898774469E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -2370,7 +2371,7 @@
         <v>7.0210237436337086E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -2390,7 +2391,7 @@
         <v>2.7643405357404942E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -2410,7 +2411,7 @@
         <v>7.0972174419790299E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -2430,7 +2431,7 @@
         <v>8.1750240600841753E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -2450,7 +2451,7 @@
         <v>6.0596521927828988E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -2470,7 +2471,7 @@
         <v>0.27273208425997925</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -2490,7 +2491,7 @@
         <v>4.1964158584099617E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -2510,9 +2511,9 @@
         <v>8.2067490551255673E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B17" s="4">
         <v>7985</v>
@@ -2529,10 +2530,10 @@
         <v>6.0004123669864205E-2</v>
       </c>
       <c r="G17" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -2552,14 +2553,14 @@
         <v>3.5264629027100369E-2</v>
       </c>
       <c r="G18" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -2578,19 +2579,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2599,11 +2600,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2623,13 +2624,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -2647,7 +2648,7 @@
         <v>6.4771018070702971E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -2667,10 +2668,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2690,7 +2691,7 @@
         <v>4.5767404114799966E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -2710,7 +2711,7 @@
         <v>5.4340261079882567E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -2730,7 +2731,7 @@
         <v>7.0595916533391617E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -2750,10 +2751,10 @@
         <v>2.3356922458284621E-2</v>
       </c>
       <c r="G10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -2773,7 +2774,7 @@
         <v>7.1650048300939045E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -2793,7 +2794,7 @@
         <v>8.278473203037609E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -2813,7 +2814,7 @@
         <v>6.154756540513466E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -2833,7 +2834,7 @@
         <v>0.27547992518092568</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -2853,7 +2854,7 @@
         <v>4.1810147688887342E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -2873,9 +2874,9 @@
         <v>8.2699027030539787E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B17" s="4">
         <v>7985</v>
@@ -2892,9 +2893,9 @@
         <v>6.1670352595512803E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B18" s="4">
         <v>2592</v>
@@ -2911,10 +2912,10 @@
         <v>4.2688531322334564E-2</v>
       </c>
       <c r="G18" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -2934,14 +2935,14 @@
         <v>2.0838148188288181E-2</v>
       </c>
       <c r="G19" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -2960,19 +2961,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2981,11 +2982,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -3005,13 +3006,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -3029,7 +3030,7 @@
         <v>6.7493665556425095E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -3049,7 +3050,7 @@
         <v>4.4226784083412921E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3069,7 +3070,7 @@
         <v>5.3773499708229838E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -3089,7 +3090,7 @@
         <v>7.515446180328153E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -3109,7 +3110,7 @@
         <v>2.4549570963454139E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -3129,7 +3130,7 @@
         <v>6.5506371764126881E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -3149,7 +3150,7 @@
         <v>8.0994630601094908E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -3169,7 +3170,7 @@
         <v>5.717689352679161E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -3189,7 +3190,7 @@
         <v>0.27435844197385051</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -3209,10 +3210,10 @@
         <v>5.7932976715717323E-2</v>
       </c>
       <c r="G14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -3232,9 +3233,9 @@
         <v>7.6734673265525633E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B16" s="4">
         <v>7985</v>
@@ -3251,9 +3252,9 @@
         <v>5.9997198687279707E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B17" s="4">
         <v>2592</v>
@@ -3270,7 +3271,7 @@
         <v>5.613317714386043E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -3290,14 +3291,14 @@
         <v>5.9676542069492739E-3</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -3316,19 +3317,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3337,11 +3338,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -3361,13 +3362,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -3385,7 +3386,7 @@
         <v>6.5031698059428725E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -3405,7 +3406,7 @@
         <v>4.5755241555266474E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3425,7 +3426,7 @@
         <v>5.3035324240180863E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -3445,7 +3446,7 @@
         <v>6.2321436288596696E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -3465,7 +3466,7 @@
         <v>2.5721293919746736E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -3485,7 +3486,7 @@
         <v>6.6111974016382219E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -3505,7 +3506,7 @@
         <v>7.8543953918109949E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -3525,7 +3526,7 @@
         <v>5.5424812925005167E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -3545,7 +3546,7 @@
         <v>0.28455069407835992</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -3565,7 +3566,7 @@
         <v>5.7269536496004629E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -3585,12 +3586,12 @@
         <v>6.2192745387710968E-2</v>
       </c>
       <c r="G15" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B16" s="4">
         <v>7985</v>
@@ -3607,9 +3608,9 @@
         <v>6.0512475484777541E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B17" s="4">
         <v>2592</v>
@@ -3626,7 +3627,7 @@
         <v>6.0428896971241444E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -3646,14 +3647,14 @@
         <v>2.3099916659188632E-2</v>
       </c>
       <c r="G18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -3672,19 +3673,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3692,15 +3693,15 @@
         <v>45174</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -3720,13 +3721,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -3744,7 +3745,7 @@
         <v>6.4294412817780491E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -3764,7 +3765,7 @@
         <v>4.2327782308852681E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3784,7 +3785,7 @@
         <v>4.8066594061314354E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -3804,7 +3805,7 @@
         <v>4.7545680757693339E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -3824,10 +3825,10 @@
         <v>2.0933808954965914E-2</v>
       </c>
       <c r="G9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -3847,7 +3848,7 @@
         <v>6.2541114121003161E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -3867,7 +3868,7 @@
         <v>9.6892668634075238E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -3887,7 +3888,7 @@
         <v>5.7877019037324964E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -3907,7 +3908,7 @@
         <v>0.32035199110374851</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -3927,7 +3928,7 @@
         <v>5.0216698145648303E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -3947,9 +3948,9 @@
         <v>5.6355004449039833E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B16" s="4">
         <v>7985</v>
@@ -3966,9 +3967,9 @@
         <v>5.4111488686503166E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B17" s="4">
         <v>2592</v>
@@ -3985,7 +3986,7 @@
         <v>5.3502023221771881E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -4005,14 +4006,14 @@
         <v>2.4983713700278146E-2</v>
       </c>
       <c r="G18" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -4031,19 +4032,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4051,15 +4052,15 @@
         <v>45181</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -4079,13 +4080,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -4103,7 +4104,7 @@
         <v>6.8773867335744462E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -4123,7 +4124,7 @@
         <v>4.0474389148844499E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4143,7 +4144,7 @@
         <v>5.0223734229621515E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -4163,7 +4164,7 @@
         <v>4.777576871736245E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -4183,7 +4184,7 @@
         <v>2.20343620617642E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -4203,7 +4204,7 @@
         <v>6.7320779245373941E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -4223,7 +4224,7 @@
         <v>9.7899189116396654E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -4243,7 +4244,7 @@
         <v>6.1524707672223386E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -4263,7 +4264,7 @@
         <v>0.30307205776571089</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -4283,7 +4284,7 @@
         <v>4.9300310457892405E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -4303,12 +4304,12 @@
         <v>5.3207570879975172E-2</v>
       </c>
       <c r="G15" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B16" s="4">
         <v>7985</v>
@@ -4325,9 +4326,9 @@
         <v>5.3766235631743688E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B17" s="4">
         <f>2592+518</f>
@@ -4345,10 +4346,10 @@
         <v>6.0411746402755095E-2</v>
       </c>
       <c r="G17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -4368,14 +4369,14 @@
         <v>2.4215281334591506E-2</v>
       </c>
       <c r="G18" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -4394,19 +4395,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4415,11 +4416,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -4439,13 +4440,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -4463,7 +4464,7 @@
         <v>7.5388858261955974E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -4483,7 +4484,7 @@
         <v>3.9523110895327923E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4503,7 +4504,7 @@
         <v>4.8570820994094897E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -4523,7 +4524,7 @@
         <v>4.8292602917887145E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -4543,7 +4544,7 @@
         <v>2.2537027580548222E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -4563,7 +4564,7 @@
         <v>6.4473185206724209E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -4584,10 +4585,10 @@
         <v>9.2132818731478328E-2</v>
       </c>
       <c r="G11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -4607,7 +4608,7 @@
         <v>5.6662666219249563E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -4627,7 +4628,7 @@
         <v>0.31354774543321895</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -4647,7 +4648,7 @@
         <v>4.8638599830828522E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -4667,9 +4668,9 @@
         <v>5.0352343390944652E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B16" s="4">
         <v>7985</v>
@@ -4686,9 +4687,9 @@
         <v>5.7020816464431016E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B17" s="4">
         <f>2592+518</f>
@@ -4706,7 +4707,7 @@
         <v>5.8636901004402824E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -4726,11 +4727,11 @@
         <v>2.4222503068907664E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -4749,19 +4750,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4770,11 +4771,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -4794,11 +4795,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -4818,7 +4819,7 @@
         <v>7.3599957457792853E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -4838,13 +4839,13 @@
         <v>5.1769287799937502E-2</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4864,7 +4865,7 @@
         <v>7.4285307188982241E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -4884,7 +4885,7 @@
         <v>6.4209001048896777E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -4904,7 +4905,7 @@
         <v>1.0944495500497694E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -4924,7 +4925,7 @@
         <v>4.5109517096649482E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -4944,7 +4945,7 @@
         <v>4.3612908690632758E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -4964,7 +4965,7 @@
         <v>5.5193596129185007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -4984,7 +4985,7 @@
         <v>1.5714816552836242E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -5004,7 +5005,7 @@
         <v>9.3811129362162016E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -5024,7 +5025,7 @@
         <v>0.10516080536894222</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -5044,7 +5045,7 @@
         <v>0.14225533235211932</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -5064,7 +5065,7 @@
         <v>2.3199076692122532E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -5084,7 +5085,7 @@
         <v>1.6088278974467244E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -5103,7 +5104,7 @@
         <v>5.020952053446999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -5123,7 +5124,7 @@
         <v>0.13222953357978273</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -5143,14 +5144,14 @@
         <v>2.6074356705231721E-3</v>
       </c>
       <c r="G21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="B22" s="4"/>
       <c r="E22" s="3"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="B23" s="4"/>
       <c r="D23">
         <f>SUM(D5:D21)</f>
@@ -5169,19 +5170,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5190,11 +5191,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -5214,13 +5215,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -5238,7 +5239,7 @@
         <v>8.1189055337625701E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -5258,7 +5259,7 @@
         <v>3.9938157495499671E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -5278,7 +5279,7 @@
         <v>4.605549111280912E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -5298,7 +5299,7 @@
         <v>5.1111235277349447E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -5318,7 +5319,7 @@
         <v>2.2029392669983168E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -5338,7 +5339,7 @@
         <v>6.0931322788320003E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -5358,7 +5359,7 @@
         <v>0.10703141735608176</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -5378,7 +5379,7 @@
         <v>5.3678383564611722E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -5398,10 +5399,10 @@
         <v>0.24364168864768404</v>
       </c>
       <c r="G13" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -5421,7 +5422,7 @@
         <v>4.772650128274758E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -5441,9 +5442,9 @@
         <v>4.7826753897163558E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B16" s="4">
         <v>7985</v>
@@ -5460,9 +5461,9 @@
         <v>5.4915656989490642E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B17" s="4">
         <f>2592+518</f>
@@ -5480,7 +5481,7 @@
         <v>5.4188433410625132E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -5500,14 +5501,14 @@
         <v>8.9736510170008318E-2</v>
       </c>
       <c r="G18" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -5526,19 +5527,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5547,11 +5548,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -5571,13 +5572,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -5595,7 +5596,7 @@
         <v>8.1165827308386396E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -5615,7 +5616,7 @@
         <v>3.745850570612011E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -5635,7 +5636,7 @@
         <v>4.6136723450257648E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -5655,7 +5656,7 @@
         <v>4.847468926269622E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -5675,7 +5676,7 @@
         <v>2.2421816133002266E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -5695,7 +5696,7 @@
         <v>5.6460679364015103E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -5715,7 +5716,7 @@
         <v>0.10966970308927836</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -5735,7 +5736,7 @@
         <v>5.8112662960918014E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -5755,7 +5756,7 @@
         <v>0.23787268980366683</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -5775,7 +5776,7 @@
         <v>4.8908624427685003E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -5795,9 +5796,9 @@
         <v>4.8822105606373109E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B16" s="4">
         <v>7985</v>
@@ -5814,9 +5815,9 @@
         <v>5.428026479532666E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B17" s="4">
         <f>2592+518+820</f>
@@ -5834,10 +5835,10 @@
         <v>7.1185192628849203E-2</v>
       </c>
       <c r="G17" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -5857,14 +5858,14 @@
         <v>7.903051546342485E-2</v>
       </c>
       <c r="G18" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -5883,19 +5884,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5904,11 +5905,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -5928,13 +5929,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -5952,7 +5953,7 @@
         <v>7.9461181023247729E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -5972,7 +5973,7 @@
         <v>3.7887234775697685E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -5992,7 +5993,7 @@
         <v>4.6810673090857284E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -6012,7 +6013,7 @@
         <v>4.8608638448791909E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -6032,7 +6033,7 @@
         <v>2.2615358784701545E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -6052,7 +6053,7 @@
         <v>5.4288682781101202E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6072,9 +6073,9 @@
         <v>0.10850846297095845</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B12" s="4">
         <v>13763</v>
@@ -6091,10 +6092,10 @@
         <v>4.9939460795092316E-2</v>
       </c>
       <c r="G12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -6114,7 +6115,7 @@
         <v>5.8453334975651854E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -6134,10 +6135,10 @@
         <v>0.22019620867452624</v>
       </c>
       <c r="G14" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -6157,7 +6158,7 @@
         <v>4.7350446565908672E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -6177,9 +6178,9 @@
         <v>4.8857318216875771E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B17" s="4">
         <v>7985</v>
@@ -6196,9 +6197,9 @@
         <v>5.3961057964620737E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B18" s="4">
         <f>2592+518+820</f>
@@ -6216,7 +6217,7 @@
         <v>7.1280596700311963E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -6236,14 +6237,14 @@
         <v>5.1781344231656576E-2</v>
       </c>
       <c r="G19" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -6262,19 +6263,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6283,11 +6284,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -6307,13 +6308,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -6331,7 +6332,7 @@
         <v>8.2145562380889478E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -6351,7 +6352,7 @@
         <v>3.7997483495581956E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -6371,7 +6372,7 @@
         <v>4.1400854184288127E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -6391,7 +6392,7 @@
         <v>4.9879996208092192E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -6411,7 +6412,7 @@
         <v>2.1621223770681656E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -6431,7 +6432,7 @@
         <v>5.8667508772525093E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6451,9 +6452,9 @@
         <v>9.7368837289661045E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B12" s="4">
         <v>13763</v>
@@ -6470,7 +6471,7 @@
         <v>5.0865958891056662E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -6490,10 +6491,10 @@
         <v>5.3990575751827981E-2</v>
       </c>
       <c r="G13" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -6513,10 +6514,10 @@
         <v>0.20202680091072436</v>
       </c>
       <c r="G14" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -6536,7 +6537,7 @@
         <v>4.9143847151590751E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -6556,12 +6557,12 @@
         <v>3.9962631267532134E-2</v>
       </c>
       <c r="G16" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B17" s="4">
         <f>7985+1084</f>
@@ -6579,12 +6580,12 @@
         <v>6.4827952268418712E-2</v>
       </c>
       <c r="G17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B18" s="4">
         <f>2592+518+820</f>
@@ -6602,7 +6603,7 @@
         <v>6.947419514533125E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -6622,14 +6623,14 @@
         <v>8.0626572511798514E-2</v>
       </c>
       <c r="G19" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -6648,19 +6649,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6669,11 +6670,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -6693,13 +6694,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -6717,7 +6718,7 @@
         <v>8.6994282981609231E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -6737,7 +6738,7 @@
         <v>3.8058819057815718E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -6757,7 +6758,7 @@
         <v>4.0573085612657607E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -6777,7 +6778,7 @@
         <v>4.3430157664768855E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -6797,7 +6798,7 @@
         <v>2.0199401398261096E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -6817,7 +6818,7 @@
         <v>5.6918643367639743E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6837,9 +6838,9 @@
         <v>8.4545740006486042E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B12" s="4">
         <v>13763</v>
@@ -6856,7 +6857,7 @@
         <v>4.9281424661612651E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -6876,10 +6877,10 @@
         <v>5.0030691969434375E-2</v>
       </c>
       <c r="G13" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -6899,7 +6900,7 @@
         <v>0.22715534273841517</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -6919,7 +6920,7 @@
         <v>4.3374191166398485E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -6939,9 +6940,9 @@
         <v>3.9187953510331955E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B17" s="4">
         <f>7985+1084</f>
@@ -6959,9 +6960,9 @@
         <v>7.0063981341213902E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B18" s="4">
         <f>2592+518+820</f>
@@ -6979,7 +6980,7 @@
         <v>6.8679897902566747E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -6999,14 +7000,14 @@
         <v>8.150638662078849E-2</v>
       </c>
       <c r="G19" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -7025,19 +7026,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7046,11 +7047,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -7070,13 +7071,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -7094,7 +7095,7 @@
         <v>8.9802934957088798E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -7114,7 +7115,7 @@
         <v>3.7066986279735162E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -7134,7 +7135,7 @@
         <v>4.0956064876211534E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -7154,7 +7155,7 @@
         <v>4.2953738832032747E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -7174,7 +7175,7 @@
         <v>1.8876408636510588E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -7194,7 +7195,7 @@
         <v>5.9095307277153834E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -7214,9 +7215,9 @@
         <v>8.6210633003389769E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B12" s="4">
         <f>13763+6317</f>
@@ -7234,10 +7235,10 @@
         <v>6.9716730968080357E-2</v>
       </c>
       <c r="G12" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -7257,7 +7258,7 @@
         <v>4.504199489270571E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -7277,7 +7278,7 @@
         <v>0.22747551214935219</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -7297,7 +7298,7 @@
         <v>4.3629959102058545E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -7317,9 +7318,9 @@
         <v>3.9527783595118271E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B17" s="4">
         <f>7985+1084</f>
@@ -7337,9 +7338,9 @@
         <v>6.9177479653111482E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B18" s="4">
         <f>2592+518+820</f>
@@ -7357,7 +7358,7 @@
         <v>7.0027983676258052E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -7377,14 +7378,14 @@
         <v>6.0440482101192905E-2</v>
       </c>
       <c r="G19" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -7403,19 +7404,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7424,11 +7425,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -7448,13 +7449,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -7472,7 +7473,7 @@
         <v>8.6206866795462078E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -7492,7 +7493,7 @@
         <v>4.3315041166930184E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -7512,7 +7513,7 @@
         <v>3.8668365206874888E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -7532,7 +7533,7 @@
         <v>4.4705542676157312E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -7552,7 +7553,7 @@
         <v>1.7865489961984695E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -7572,7 +7573,7 @@
         <v>5.5812367058372454E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -7592,9 +7593,9 @@
         <v>0.12308335400645683</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B12" s="4">
         <f>13763+6317</f>
@@ -7612,7 +7613,7 @@
         <v>5.77659753769975E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -7632,7 +7633,7 @@
         <v>4.3499312533629576E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -7652,7 +7653,7 @@
         <v>0.22415604405455763</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -7672,7 +7673,7 @@
         <v>4.0811908476403029E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -7692,9 +7693,9 @@
         <v>3.9417597362396521E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B17" s="4">
         <f>7985+1084</f>
@@ -7712,9 +7713,9 @@
         <v>6.2655425230954853E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B18" s="4">
         <f>2592+518+820</f>
@@ -7732,7 +7733,7 @@
         <v>6.6128682566689259E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -7752,14 +7753,14 @@
         <v>5.5908027526133067E-2</v>
       </c>
       <c r="G19" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -7775,19 +7776,19 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C18A242-0910-4E92-A461-DA397E54CBAB}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="B3">
         <v>63467</v>
@@ -7797,9 +7798,9 @@
         <v>126.934</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="B4">
         <v>938</v>
@@ -7809,9 +7810,9 @@
         <v>1.8760000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="B5">
         <v>938</v>
@@ -7821,9 +7822,9 @@
         <v>1.8760000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="B6">
         <v>37975</v>
@@ -7833,9 +7834,9 @@
         <v>75.95</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="B7">
         <v>464150</v>
@@ -7845,9 +7846,9 @@
         <v>928.30000000000007</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="B8">
         <v>1152985</v>
@@ -7857,9 +7858,9 @@
         <v>2305.9700000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="B9">
         <v>1596452</v>
@@ -7869,9 +7870,9 @@
         <v>3192.904</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="B10">
         <v>227269</v>
@@ -7881,9 +7882,9 @@
         <v>454.53800000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="B11">
         <v>949600</v>
@@ -7893,9 +7894,9 @@
         <v>1899.2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="B12">
         <v>949600</v>
@@ -7905,9 +7906,9 @@
         <v>1899.2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="B13">
         <v>2032848</v>
@@ -7917,9 +7918,9 @@
         <v>4065.6959999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="B14">
         <v>2619938</v>
@@ -7929,7 +7930,7 @@
         <v>5239.8760000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3">
       <c r="C16" s="2">
         <f>SUM(C3:C15)</f>
         <v>20192.32</v>
@@ -7944,7 +7945,7 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E270A1E4-8160-48C8-BABC-214DD704FB6A}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7956,19 +7957,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7977,11 +7978,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -8001,11 +8002,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -8025,7 +8026,7 @@
         <v>7.1319595387765874E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -8045,7 +8046,7 @@
         <v>4.2299060048999894E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -8065,7 +8066,7 @@
         <v>6.6733550160477273E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -8085,7 +8086,7 @@
         <v>6.4828782189368855E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -8105,10 +8106,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -8128,7 +8129,7 @@
         <v>4.9397467199217684E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -8148,7 +8149,7 @@
         <v>4.6303141741729427E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -8168,11 +8169,12 @@
         <v>4.8514789623390946E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>15</v>
       </c>
       <c r="B13" s="4">
+        <f>1727-863-216-648</f>
         <v>0</v>
       </c>
       <c r="C13" s="2">
@@ -8187,10 +8189,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -8210,7 +8212,7 @@
         <v>0.10064983774452103</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -8230,7 +8232,7 @@
         <v>0.11037153176004473</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -8250,7 +8252,7 @@
         <v>0.14256133691968101</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -8270,7 +8272,7 @@
         <v>2.225294311911221E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -8290,10 +8292,10 @@
         <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -8312,7 +8314,7 @@
         <v>5.6026574515047389E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -8332,7 +8334,7 @@
         <v>0.12744900593580041</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -8352,14 +8354,14 @@
         <v>5.1292383654843295E-2</v>
       </c>
       <c r="G21" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="B22" s="4"/>
       <c r="E22" s="3"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="B23" s="4"/>
       <c r="D23">
         <f>SUM(D5:D21)</f>
@@ -8378,19 +8380,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8399,11 +8401,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -8423,13 +8425,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4">
         <v>4326</v>
@@ -8446,10 +8448,10 @@
         <v>5.083701401317612E-2</v>
       </c>
       <c r="G5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -8469,7 +8471,7 @@
         <v>7.1350770455332391E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -8489,7 +8491,7 @@
         <v>4.231754972281055E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -8509,7 +8511,7 @@
         <v>6.6762720585854696E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -8529,7 +8531,7 @@
         <v>6.4857120006682881E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -8549,7 +8551,7 @@
         <v>4.9419059713437338E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -8569,7 +8571,7 @@
         <v>4.6323381671085337E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -8589,7 +8591,7 @@
         <v>4.8535996303494235E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -8609,7 +8611,7 @@
         <v>0.1006938335843065</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -8629,7 +8631,7 @@
         <v>0.11041977712573044</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -8649,7 +8651,7 @@
         <v>0.14262365302350466</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -8669,7 +8671,7 @@
         <v>2.2262670277567332E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -8688,7 +8690,7 @@
         <v>5.6051064730345594E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -8708,7 +8710,7 @@
         <v>0.12750471617012987</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -8728,14 +8730,14 @@
         <v>4.0672616542044231E-5</v>
       </c>
       <c r="G19" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -8754,19 +8756,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8775,11 +8777,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -8799,13 +8801,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4">
         <v>4326</v>
@@ -8822,7 +8824,7 @@
         <v>4.2099644043829064E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -8842,7 +8844,7 @@
         <v>6.4267524587005173E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -8862,7 +8864,7 @@
         <v>4.5925920052905481E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -8882,7 +8884,7 @@
         <v>6.6215615610525996E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -8902,7 +8904,7 @@
         <v>6.1042361492457696E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -8922,7 +8924,7 @@
         <v>3.9737538109024119E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -8942,7 +8944,7 @@
         <v>3.4706000959483063E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -8962,7 +8964,7 @@
         <v>6.0556428084807865E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -8982,7 +8984,7 @@
         <v>0.1044141256688586</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -9002,7 +9004,7 @@
         <v>0.10009219034773438</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -9022,7 +9024,7 @@
         <v>0.17764052442068692</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -9042,7 +9044,7 @@
         <v>1.9098633103246627E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -9061,7 +9063,7 @@
         <v>3.8062245698182916E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -9081,13 +9083,13 @@
         <v>0.14465583839010121</v>
       </c>
       <c r="G18" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="H18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -9107,14 +9109,14 @@
         <v>1.4854094311509637E-3</v>
       </c>
       <c r="G19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -9133,19 +9135,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9154,11 +9156,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -9178,13 +9180,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4">
         <v>4326</v>
@@ -9201,7 +9203,7 @@
         <v>4.2564270044788688E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -9221,13 +9223,13 @@
         <v>5.9966078371780168E-2</v>
       </c>
       <c r="G6" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="H6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -9247,7 +9249,7 @@
         <v>4.3400571281146536E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -9267,7 +9269,7 @@
         <v>6.6612575436105839E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -9287,7 +9289,7 @@
         <v>6.0589245186324463E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -9307,7 +9309,7 @@
         <v>3.6667317002348522E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -9327,7 +9329,7 @@
         <v>3.470730263780205E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -9347,7 +9349,7 @@
         <v>5.7922460594562963E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -9367,7 +9369,7 @@
         <v>0.10794801516561595</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -9387,7 +9389,7 @@
         <v>9.9060160957756924E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -9407,7 +9409,7 @@
         <v>0.19914026103656915</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -9427,7 +9429,7 @@
         <v>1.8079186953024545E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -9446,7 +9448,7 @@
         <v>3.3902861858966939E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -9466,7 +9468,7 @@
         <v>0.13519060473399733</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -9486,14 +9488,14 @@
         <v>4.2490887392100003E-3</v>
       </c>
       <c r="G19" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -9512,19 +9514,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9533,11 +9535,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -9557,13 +9559,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -9581,10 +9583,10 @@
         <v>7.788423704361544E-2</v>
       </c>
       <c r="G5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -9604,7 +9606,7 @@
         <v>5.5816259099599239E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -9624,7 +9626,7 @@
         <v>4.6030903074073204E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -9644,7 +9646,7 @@
         <v>5.858741556942465E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -9664,7 +9666,7 @@
         <v>6.988931591514036E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -9684,7 +9686,7 @@
         <v>3.5488596550605114E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -9704,7 +9706,7 @@
         <v>3.3416777189733342E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -9724,7 +9726,7 @@
         <v>6.8205621992278059E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -9744,7 +9746,7 @@
         <v>0.10814477777826351</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -9764,10 +9766,10 @@
         <v>6.9897712357052125E-2</v>
       </c>
       <c r="G14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -9787,7 +9789,7 @@
         <v>0.18750042960722105</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -9807,10 +9809,10 @@
         <v>0</v>
       </c>
       <c r="G16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -9829,7 +9831,7 @@
         <v>3.8823235055846284E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -9849,7 +9851,7 @@
         <v>0.13372377133755631</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -9869,14 +9871,14 @@
         <v>1.6590947429591184E-2</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="B21" s="4"/>
       <c r="D21">
         <f>SUM(D5:D19)</f>
@@ -9895,19 +9897,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9916,11 +9918,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -9940,13 +9942,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -9964,7 +9966,7 @@
         <v>7.9209777541105267E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -9984,7 +9986,7 @@
         <v>5.732355737466692E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -10004,7 +10006,7 @@
         <v>4.6820177499256363E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -10024,7 +10026,7 @@
         <v>6.0897344785313973E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -10044,7 +10046,7 @@
         <v>7.2156541231088861E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -10064,7 +10066,7 @@
         <v>3.5080304713496831E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -10084,7 +10086,7 @@
         <v>3.3042050399742715E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -10104,7 +10106,7 @@
         <v>6.7777192666563804E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -10124,7 +10126,7 @@
         <v>0.10610010043673311</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -10144,7 +10146,7 @@
         <v>7.0126392348995314E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -10164,7 +10166,7 @@
         <v>0.18211134183776867</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -10183,7 +10185,7 @@
         <v>3.8987066559362987E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -10203,10 +10205,10 @@
         <v>9.9008364204680968E-2</v>
       </c>
       <c r="G17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -10226,14 +10228,14 @@
         <v>5.1359788401224224E-2</v>
       </c>
       <c r="G18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
@@ -10252,19 +10254,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10273,11 +10275,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -10297,13 +10299,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4">
         <f>4326+2424</f>
@@ -10321,7 +10323,7 @@
         <v>7.8460066748204521E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -10341,7 +10343,7 @@
         <v>5.2240048013344149E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -10361,7 +10363,7 @@
         <v>4.901846779378928E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -10381,7 +10383,7 @@
         <v>6.0292590715831526E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -10401,7 +10403,7 @@
         <v>7.0878565844423577E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -10421,7 +10423,7 @@
         <v>3.4327445208782066E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -10441,7 +10443,7 @@
         <v>3.3770921645260001E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -10461,7 +10463,7 @@
         <v>6.430779772866238E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -10481,7 +10483,7 @@
         <v>9.7399295780519424E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -10501,7 +10503,7 @@
         <v>7.2390497082646305E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -10521,7 +10523,7 @@
         <v>0.18935106420135733</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -10541,10 +10543,10 @@
         <v>5.0287643889129451E-2</v>
       </c>
       <c r="G16" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -10564,7 +10566,7 @@
         <v>0.1078290187756383</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -10584,14 +10586,14 @@
         <v>3.9446576572411539E-2</v>
       </c>
       <c r="G18" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="B19" s="4"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="B20" s="4"/>
       <c r="D20">
         <f>SUM(D5:D18)</f>
